--- a/Code/Battery_Monitor/voltage_sensor_analysis.xlsx
+++ b/Code/Battery_Monitor/voltage_sensor_analysis.xlsx
@@ -135,7 +135,7 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -166,7 +166,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="pt-PT"/>
         </a:p>
@@ -261,7 +261,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="pt-PT"/>
                 </a:p>
@@ -458,7 +458,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
@@ -524,7 +524,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
